--- a/1_Data/3. GTAPAEZ_Deforestation_coefficient/A-3_Database_Forest_Intensity_GTAPAEZ_shocks_LU_ctl.xlsx
+++ b/1_Data/3. GTAPAEZ_Deforestation_coefficient/A-3_Database_Forest_Intensity_GTAPAEZ_shocks_LU_ctl.xlsx
@@ -1067,12 +1067,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1082,22 +1082,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Peru#AEZ11#ctl</t>
+          <t>DRC#AEZ12#ctl</t>
         </is>
       </c>
       <c r="E5" s="1">
-        <v>33300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1107,22 +1107,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Brazil#AEZ4#ctl</t>
+          <t>Peru#AEZ11#ctl</t>
         </is>
       </c>
       <c r="E6" s="1">
-        <v>153600</v>
+        <v>33300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1132,22 +1132,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ivory Coast#AEZ6#ctl</t>
+          <t>Brazil#AEZ4#ctl</t>
         </is>
       </c>
       <c r="E7" s="1">
-        <v>67400</v>
+        <v>153600</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1157,22 +1157,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bolivia#AEZ5#ctl</t>
+          <t>Ivory Coast#AEZ6#ctl</t>
         </is>
       </c>
       <c r="E8" s="1">
-        <v>100200</v>
+        <v>67400</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ghana#AEZ4#ctl</t>
+          <t>Angola#AEZ3#ctl</t>
         </is>
       </c>
       <c r="E9" s="1">
-        <v>29700</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AEZ7</t>
+          <t>AEZ5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Argentina#AEZ7#ctl</t>
+          <t>Bolivia#AEZ5#ctl</t>
         </is>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
+        <v>100200</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AEZ2</t>
+          <t>AEZ4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1232,22 +1232,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paraguay#AEZ2#ctl</t>
+          <t>Ghana#AEZ4#ctl</t>
         </is>
       </c>
       <c r="E11" s="1">
-        <v>0</v>
+        <v>29700</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1257,22 +1257,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ghana#AEZ3#ctl</t>
+          <t>Argentina#AEZ7#ctl</t>
         </is>
       </c>
       <c r="E12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AEZ9</t>
+          <t>AEZ2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bolivia#AEZ9#ctl</t>
+          <t>Paraguay#AEZ2#ctl</t>
         </is>
       </c>
       <c r="E13" s="1">
@@ -1292,12 +1292,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1307,22 +1307,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Indonesia#AEZ11#ctl</t>
+          <t>Ghana#AEZ3#ctl</t>
         </is>
       </c>
       <c r="E14" s="1">
-        <v>13200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AEZ1</t>
+          <t>AEZ9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Brazil#AEZ1#ctl</t>
+          <t>Bolivia#AEZ9#ctl</t>
         </is>
       </c>
       <c r="E15" s="1">
@@ -1342,12 +1342,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1357,17 +1357,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Peru#AEZ4#ctl</t>
+          <t>DRC#AEZ6#ctl</t>
         </is>
       </c>
       <c r="E16" s="1">
-        <v>500</v>
+        <v>106800</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1382,22 +1382,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Colombia#AEZ8#ctl</t>
+          <t>Angola#AEZ8#ctl</t>
         </is>
       </c>
       <c r="E17" s="1">
-        <v>6200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AEZ13</t>
+          <t>AEZ11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Argentina#AEZ13#ctl</t>
+          <t>Indonesia#AEZ11#ctl</t>
         </is>
       </c>
       <c r="E18" s="1">
-        <v>0</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paraguay#AEZ12#ctl</t>
+          <t>Brazil#AEZ1#ctl</t>
         </is>
       </c>
       <c r="E19" s="1">
@@ -1442,12 +1442,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AngDRC</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AEZ10</t>
+          <t>AEZ4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1457,22 +1457,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AngDRC#AEZ10#ctl</t>
+          <t>Peru#AEZ4#ctl</t>
         </is>
       </c>
       <c r="E20" s="1">
-        <v>182100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AEZ16</t>
+          <t>AEZ8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1482,22 +1482,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Argentina#AEZ16#ctl</t>
+          <t>Colombia#AEZ8#ctl</t>
         </is>
       </c>
       <c r="E21" s="1">
-        <v>6600</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AngDRC</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1507,22 +1507,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AngDRC#AEZ11#ctl</t>
+          <t>Argentina#AEZ13#ctl</t>
         </is>
       </c>
       <c r="E22" s="1">
-        <v>199900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AEZ2</t>
+          <t>AEZ12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Brazil#AEZ2#ctl</t>
+          <t>Paraguay#AEZ12#ctl</t>
         </is>
       </c>
       <c r="E23" s="1">
@@ -1542,7 +1542,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1557,22 +1557,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Brazil#AEZ5#ctl</t>
+          <t>DRC#AEZ5#ctl</t>
         </is>
       </c>
       <c r="E24" s="1">
-        <v>1151500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AEZ2</t>
+          <t>AEZ16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1582,22 +1582,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Colombia#AEZ2#ctl</t>
+          <t>Argentina#AEZ16#ctl</t>
         </is>
       </c>
       <c r="E25" s="1">
-        <v>40800</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Argentina#AEZ11#ctl</t>
+          <t>Brazil#AEZ2#ctl</t>
         </is>
       </c>
       <c r="E26" s="1">
@@ -1617,7 +1617,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1632,22 +1632,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Colombia#AEZ5#ctl</t>
+          <t>Brazil#AEZ5#ctl</t>
         </is>
       </c>
       <c r="E27" s="1">
-        <v>419700</v>
+        <v>1151500</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1657,22 +1657,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Brazil#AEZ11#ctl</t>
+          <t>Colombia#AEZ2#ctl</t>
         </is>
       </c>
       <c r="E28" s="1">
-        <v>1900</v>
+        <v>40800</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AEZ1</t>
+          <t>AEZ11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1682,22 +1682,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Peru#AEZ1#ctl</t>
+          <t>Argentina#AEZ11#ctl</t>
         </is>
       </c>
       <c r="E29" s="1">
-        <v>1200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AngDRC</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1707,22 +1707,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AngDRC#AEZ3#ctl</t>
+          <t>Colombia#AEZ5#ctl</t>
         </is>
       </c>
       <c r="E30" s="1">
-        <v>1900</v>
+        <v>419700</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AEZ7</t>
+          <t>AEZ11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1732,22 +1732,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Peru#AEZ7#ctl</t>
+          <t>Brazil#AEZ11#ctl</t>
         </is>
       </c>
       <c r="E31" s="1">
-        <v>14000</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1757,22 +1757,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Paraguay#AEZ11#ctl</t>
+          <t>Peru#AEZ1#ctl</t>
         </is>
       </c>
       <c r="E32" s="1">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Indonesia#AEZ4#ctl</t>
+          <t>Peru#AEZ7#ctl</t>
         </is>
       </c>
       <c r="E33" s="1">
-        <v>49300</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1807,22 +1807,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Argentina#AEZ5#ctl</t>
+          <t>Paraguay#AEZ11#ctl</t>
         </is>
       </c>
       <c r="E34" s="1">
-        <v>1800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1832,22 +1832,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Peru#AEZ5#ctl</t>
+          <t>Indonesia#AEZ4#ctl</t>
         </is>
       </c>
       <c r="E35" s="1">
-        <v>4100</v>
+        <v>49300</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1857,22 +1857,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Colombia#AEZ6#ctl</t>
+          <t>DRC#AEZ4#ctl</t>
         </is>
       </c>
       <c r="E36" s="1">
-        <v>1657900</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Colombia#AEZ12#ctl</t>
+          <t>Argentina#AEZ5#ctl</t>
         </is>
       </c>
       <c r="E37" s="1">
-        <v>211600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AEZ14</t>
+          <t>AEZ5</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Argentina#AEZ14#ctl</t>
+          <t>Peru#AEZ5#ctl</t>
         </is>
       </c>
       <c r="E38" s="1">
-        <v>0</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Malaysia#AEZ6#ctl</t>
+          <t>Colombia#AEZ6#ctl</t>
         </is>
       </c>
       <c r="E39" s="1">
-        <v>1100</v>
+        <v>1657900</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1957,22 +1957,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Peru#AEZ12#ctl</t>
+          <t>Colombia#AEZ12#ctl</t>
         </is>
       </c>
       <c r="E40" s="1">
-        <v>116700</v>
+        <v>211600</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AngDRC</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1982,22 +1982,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AngDRC#AEZ12#ctl</t>
+          <t>Argentina#AEZ14#ctl</t>
         </is>
       </c>
       <c r="E41" s="1">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AEZ7</t>
+          <t>AEZ6</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Bolivia#AEZ7#ctl</t>
+          <t>Malaysia#AEZ6#ctl</t>
         </is>
       </c>
       <c r="E42" s="1">
-        <v>8500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ7</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2032,22 +2032,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Indonesia#AEZ6#ctl</t>
+          <t>Angola#AEZ7#ctl</t>
         </is>
       </c>
       <c r="E43" s="1">
-        <v>137000</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AngDRC</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AEZ9</t>
+          <t>AEZ5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2057,22 +2057,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AngDRC#AEZ9#ctl</t>
+          <t>Angola#AEZ5#ctl</t>
         </is>
       </c>
       <c r="E44" s="1">
-        <v>3600</v>
+        <v>1989300</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2082,22 +2082,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Peru#AEZ6#ctl</t>
+          <t>Angola#AEZ10#ctl</t>
         </is>
       </c>
       <c r="E45" s="1">
-        <v>19600</v>
+        <v>186900</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Malaysia#AEZ12#ctl</t>
+          <t>Angola#AEZ1#ctl</t>
         </is>
       </c>
       <c r="E46" s="1">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Bolivia#AEZ12#ctl</t>
+          <t>Peru#AEZ12#ctl</t>
         </is>
       </c>
       <c r="E47" s="1">
-        <v>16900</v>
+        <v>116700</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2157,22 +2157,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Argentina#AEZ3#ctl</t>
+          <t>Angola#AEZ11#ctl</t>
         </is>
       </c>
       <c r="E48" s="1">
-        <v>0</v>
+        <v>206400</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AEZ2</t>
+          <t>AEZ7</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2182,22 +2182,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Peru#AEZ2#ctl</t>
+          <t>Bolivia#AEZ7#ctl</t>
         </is>
       </c>
       <c r="E49" s="1">
-        <v>0</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AEZ10</t>
+          <t>AEZ6</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2207,22 +2207,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Paraguay#AEZ10#ctl</t>
+          <t>Indonesia#AEZ6#ctl</t>
         </is>
       </c>
       <c r="E50" s="1">
-        <v>0</v>
+        <v>137000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2232,11 +2232,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Paraguay#AEZ3#ctl</t>
+          <t>Angola#AEZ4#ctl</t>
         </is>
       </c>
       <c r="E51" s="1">
-        <v>0</v>
+        <v>654700</v>
       </c>
     </row>
     <row r="52">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ6</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2257,22 +2257,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Peru#AEZ3#ctl</t>
+          <t>Peru#AEZ6#ctl</t>
         </is>
       </c>
       <c r="E52" s="1">
-        <v>400</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ12</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2282,22 +2282,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Indonesia#AEZ5#ctl</t>
+          <t>Malaysia#AEZ12#ctl</t>
         </is>
       </c>
       <c r="E53" s="1">
-        <v>29400</v>
+        <v>900</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AEZ10</t>
+          <t>AEZ12</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2307,22 +2307,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Peru#AEZ10#ctl</t>
+          <t>Bolivia#AEZ12#ctl</t>
         </is>
       </c>
       <c r="E54" s="1">
-        <v>10800</v>
+        <v>16900</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2332,22 +2332,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Indonesia#AEZ12#ctl</t>
+          <t>Argentina#AEZ3#ctl</t>
         </is>
       </c>
       <c r="E55" s="1">
-        <v>87500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2357,11 +2357,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Bolivia#AEZ4#ctl</t>
+          <t>Peru#AEZ2#ctl</t>
         </is>
       </c>
       <c r="E56" s="1">
-        <v>45200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ10</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2382,22 +2382,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Paraguay#AEZ5#ctl</t>
+          <t>Paraguay#AEZ10#ctl</t>
         </is>
       </c>
       <c r="E57" s="1">
-        <v>11500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2407,22 +2407,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Colombia#AEZ11#ctl</t>
+          <t>Paraguay#AEZ3#ctl</t>
         </is>
       </c>
       <c r="E58" s="1">
-        <v>5100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AEZ9</t>
+          <t>AEZ3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Colombia#AEZ9#ctl</t>
+          <t>Peru#AEZ3#ctl</t>
         </is>
       </c>
       <c r="E59" s="1">
@@ -2442,12 +2442,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2457,22 +2457,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ghana#AEZ6#ctl</t>
+          <t>Indonesia#AEZ5#ctl</t>
         </is>
       </c>
       <c r="E60" s="1">
-        <v>5300</v>
+        <v>29400</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AEZ9</t>
+          <t>AEZ10</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2482,22 +2482,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Argentina#AEZ9#ctl</t>
+          <t>Peru#AEZ10#ctl</t>
         </is>
       </c>
       <c r="E61" s="1">
-        <v>0</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ12</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2507,17 +2507,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Bolivia#AEZ3#ctl</t>
+          <t>Indonesia#AEZ12#ctl</t>
         </is>
       </c>
       <c r="E62" s="1">
-        <v>600</v>
+        <v>87500</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AngDRC</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2532,22 +2532,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AngDRC#AEZ4#ctl</t>
+          <t>Bolivia#AEZ4#ctl</t>
         </is>
       </c>
       <c r="E63" s="1">
-        <v>643600</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AngDRC</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AEZ1</t>
+          <t>AEZ5</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,22 +2557,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AngDRC#AEZ1#ctl</t>
+          <t>Paraguay#AEZ5#ctl</t>
         </is>
       </c>
       <c r="E64" s="1">
-        <v>0</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AEZ10</t>
+          <t>AEZ11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2582,22 +2582,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Brazil#AEZ10#ctl</t>
+          <t>Colombia#AEZ11#ctl</t>
         </is>
       </c>
       <c r="E65" s="1">
-        <v>200</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ10</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2607,22 +2607,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Brazil#AEZ3#ctl</t>
+          <t>DRC#AEZ10#ctl</t>
         </is>
       </c>
       <c r="E66" s="1">
-        <v>11700</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AngDRC</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ9</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2632,22 +2632,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AngDRC#AEZ5#ctl</t>
+          <t>Colombia#AEZ9#ctl</t>
         </is>
       </c>
       <c r="E67" s="1">
-        <v>1917000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ6</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2657,22 +2657,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ivory Coast#AEZ5#ctl</t>
+          <t>Ghana#AEZ6#ctl</t>
         </is>
       </c>
       <c r="E68" s="1">
-        <v>200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AEZ8</t>
+          <t>AEZ9</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2682,22 +2682,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Bolivia#AEZ8#ctl</t>
+          <t>Argentina#AEZ9#ctl</t>
         </is>
       </c>
       <c r="E69" s="1">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AEZ15</t>
+          <t>AEZ3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Argentina#AEZ15#ctl</t>
+          <t>Bolivia#AEZ3#ctl</t>
         </is>
       </c>
       <c r="E70" s="1">
-        <v>1500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AngDRC</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ10</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2732,22 +2732,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AngDRC#AEZ6#ctl</t>
+          <t>Brazil#AEZ10#ctl</t>
         </is>
       </c>
       <c r="E71" s="1">
-        <v>106800</v>
+        <v>200</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2757,22 +2757,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ivory Coast#AEZ4#ctl</t>
+          <t>Brazil#AEZ3#ctl</t>
         </is>
       </c>
       <c r="E72" s="1">
-        <v>100</v>
+        <v>11700</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ11</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2782,22 +2782,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Argentina#AEZ4#ctl</t>
+          <t>DRC#AEZ11#ctl</t>
         </is>
       </c>
       <c r="E73" s="1">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2807,22 +2807,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Brazil#AEZ12#ctl</t>
+          <t>Angola#AEZ2#ctl</t>
         </is>
       </c>
       <c r="E74" s="1">
-        <v>55600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AEZ8</t>
+          <t>AEZ5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2832,11 +2832,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Argentina#AEZ8#ctl</t>
+          <t>Ivory Coast#AEZ5#ctl</t>
         </is>
       </c>
       <c r="E75" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="76">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AEZ10</t>
+          <t>AEZ8</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2857,22 +2857,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Bolivia#AEZ10#ctl</t>
+          <t>Bolivia#AEZ8#ctl</t>
         </is>
       </c>
       <c r="E76" s="1">
-        <v>100</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AngDRC</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AEZ8</t>
+          <t>AEZ15</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AngDRC#AEZ8#ctl</t>
+          <t>Argentina#AEZ15#ctl</t>
         </is>
       </c>
       <c r="E77" s="1">
-        <v>800</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2907,17 +2907,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Argentina#AEZ12#ctl</t>
+          <t>DRC#AEZ3#ctl</t>
         </is>
       </c>
       <c r="E78" s="1">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2932,17 +2932,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Paraguay#AEZ4#ctl</t>
+          <t>Ivory Coast#AEZ4#ctl</t>
         </is>
       </c>
       <c r="E79" s="1">
-        <v>12500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Colombia#AEZ4#ctl</t>
+          <t>Argentina#AEZ4#ctl</t>
         </is>
       </c>
       <c r="E80" s="1">
-        <v>9700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ12</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2982,22 +2982,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Indonesia#AEZ3#ctl</t>
+          <t>Brazil#AEZ12#ctl</t>
         </is>
       </c>
       <c r="E81" s="1">
-        <v>0</v>
+        <v>55600</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ8</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3007,22 +3007,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Ghana#AEZ5#ctl</t>
+          <t>Argentina#AEZ8#ctl</t>
         </is>
       </c>
       <c r="E82" s="1">
-        <v>49400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AngDRC</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AEZ7</t>
+          <t>AEZ10</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3032,22 +3032,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AngDRC#AEZ7#ctl</t>
+          <t>Bolivia#AEZ10#ctl</t>
         </is>
       </c>
       <c r="E83" s="1">
-        <v>3100</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ9</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3057,22 +3057,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Bolivia#AEZ11#ctl</t>
+          <t>DRC#AEZ9#ctl</t>
         </is>
       </c>
       <c r="E84" s="1">
-        <v>9900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AngDRC</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AEZ2</t>
+          <t>AEZ12</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AngDRC#AEZ2#ctl</t>
+          <t>Argentina#AEZ12#ctl</t>
         </is>
       </c>
       <c r="E85" s="1">
@@ -3092,12 +3092,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AEZ7</t>
+          <t>AEZ4</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3107,22 +3107,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Colombia#AEZ7#ctl</t>
+          <t>Paraguay#AEZ4#ctl</t>
         </is>
       </c>
       <c r="E86" s="1">
-        <v>11100</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AEZ9</t>
+          <t>AEZ4</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3132,17 +3132,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Peru#AEZ9#ctl</t>
+          <t>Colombia#AEZ4#ctl</t>
         </is>
       </c>
       <c r="E87" s="1">
-        <v>14900</v>
+        <v>9700</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3157,22 +3157,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Colombia#AEZ3#ctl</t>
+          <t>Indonesia#AEZ3#ctl</t>
         </is>
       </c>
       <c r="E88" s="1">
-        <v>34100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AEZ8</t>
+          <t>AEZ5</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3182,35 +3182,185 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Peru#AEZ8#ctl</t>
+          <t>Ghana#AEZ5#ctl</t>
         </is>
       </c>
       <c r="E89" s="1">
-        <v>14000</v>
+        <v>49400</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>AEZ9</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ctl</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Angola#AEZ9#ctl</t>
+        </is>
+      </c>
+      <c r="E90" s="1">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>AEZ11</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ctl</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Bolivia#AEZ11#ctl</t>
+        </is>
+      </c>
+      <c r="E91" s="1">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>AEZ7</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ctl</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Colombia#AEZ7#ctl</t>
+        </is>
+      </c>
+      <c r="E92" s="1">
+        <v>11100</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>AEZ9</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ctl</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Peru#AEZ9#ctl</t>
+        </is>
+      </c>
+      <c r="E93" s="1">
+        <v>14900</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>AEZ3</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ctl</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Colombia#AEZ3#ctl</t>
+        </is>
+      </c>
+      <c r="E94" s="1">
+        <v>34100</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>AEZ8</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ctl</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Peru#AEZ8#ctl</t>
+        </is>
+      </c>
+      <c r="E95" s="1">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>AEZ10</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>ctl</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ctl</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
         <is>
           <t>Argentina#AEZ10#ctl</t>
         </is>
       </c>
-      <c r="E90" s="1">
+      <c r="E96" s="1">
         <v>0</v>
       </c>
     </row>
